--- a/data/USMain_test.xlsx
+++ b/data/USMain_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sxj477\Documents\GitHub\SSD\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sxj477\Documents\GitHub\SSDclaude\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071AA75E-9C0A-41B3-9732-E9F8CD9508C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB02432D-F8F0-4798-BEF1-51E73F2B7219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="10800" activeTab="2" xr2:uid="{D3C4F84A-0E01-44C3-A15D-A44758EFE8C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{D3C4F84A-0E01-44C3-A15D-A44758EFE8C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>t</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>Worker-to-retiree (population growth)</t>
+  </si>
+  <si>
+    <t>2026-10-23 (review response A2: pensions only in the U.S., UK and France): calibration!D2 is public cash spending on old-age and survivors pensions in 2020, 7.366% of GDP, OECD SOCX (OECD.ELS.SPD:DSD_SOCX_AGG, public ES10, old age and survivors TP01, in cash C, % of GDP; retrieved 2026-09-30), the value in data/oecdFigure1.csv column pensionSpending (figure 1.1), over the labour share 1-B2. It was =0.101/(1-B2), 7.2 pensions plus 2.9 Medicare (MedPAC 2020 Data Book). calibration!E2 (Universal share) is 0; it was (0.029/(1-B2))/D2, the Medicare share of spending, and is inert in the US model (getEps). calibration!G2 is =39.2/49.6, the gross replacement rates of men at 1.0 and 0.5 times average earnings, OECD Pensions at a Glance 2021, table 4.1 (data/oecdFigure1.csv grr100_men, grr050_men); it was =39.2/49.2.</t>
   </si>
 </sst>
 </file>
@@ -493,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05AA8116-F26D-48D0-B2CE-7FBA20E167F1}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -509,6 +512,11 @@
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -798,19 +806,18 @@
         <v>0.3</v>
       </c>
       <c r="D2">
-        <f>0.101/(1-B2)</f>
-        <v>0.14428571428571429</v>
+        <f>0.07366/(1-B2)</f>
+        <v>0.10522857142857144</v>
       </c>
       <c r="E2">
-        <f>(0.029/(1-B2))/D2</f>
-        <v>0.28712871287128716</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>2.4430000000000001</v>
       </c>
       <c r="G2">
-        <f>39.2/49.2</f>
-        <v>0.7967479674796748</v>
+        <f>39.2/49.6</f>
+        <v>0.79032258064516137</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>14</v>

--- a/data/USMain_test.xlsx
+++ b/data/USMain_test.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sxj477\Documents\GitHub\SSDclaude\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB02432D-F8F0-4798-BEF1-51E73F2B7219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACFC2E2-98AA-4F41-8F09-F030777B3F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{D3C4F84A-0E01-44C3-A15D-A44758EFE8C0}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" activeTab="1" xr2:uid="{D3C4F84A-0E01-44C3-A15D-A44758EFE8C0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Readme" sheetId="4" r:id="rId1"/>
-    <sheet name="population" sheetId="1" r:id="rId2"/>
-    <sheet name="heterogeneity" sheetId="2" r:id="rId3"/>
-    <sheet name="calibration" sheetId="3" r:id="rId4"/>
+    <sheet name="population" sheetId="1" r:id="rId1"/>
+    <sheet name="heterogeneity" sheetId="2" r:id="rId2"/>
+    <sheet name="calibration" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>t</t>
   </si>
@@ -92,22 +91,10 @@
     <t>Universal share</t>
   </si>
   <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>Group = 0 is per construction informal workers. They are not used in the US model, but the main code relies on this type. Thus, synthetic data is filled in here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calibration targets are different for US calibration than Argentina. </t>
-  </si>
-  <si>
     <t>Average workweek</t>
   </si>
   <si>
     <t>Worker-to-retiree (population growth)</t>
-  </si>
-  <si>
-    <t>2026-10-23 (review response A2: pensions only in the U.S., UK and France): calibration!D2 is public cash spending on old-age and survivors pensions in 2020, 7.366% of GDP, OECD SOCX (OECD.ELS.SPD:DSD_SOCX_AGG, public ES10, old age and survivors TP01, in cash C, % of GDP; retrieved 2026-09-30), the value in data/oecdFigure1.csv column pensionSpending (figure 1.1), over the labour share 1-B2. It was =0.101/(1-B2), 7.2 pensions plus 2.9 Medicare (MedPAC 2020 Data Book). calibration!E2 (Universal share) is 0; it was (0.029/(1-B2))/D2, the Medicare share of spending, and is inert in the US model (getEps). calibration!G2 is =39.2/49.6, the gross replacement rates of men at 1.0 and 0.5 times average earnings, OECD Pensions at a Glance 2021, table 4.1 (data/oecdFigure1.csv grr100_men, grr050_men); it was =39.2/49.2.</t>
   </si>
 </sst>
 </file>
@@ -495,28 +482,102 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05AA8116-F26D-48D0-B2CE-7FBA20E167F1}">
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43B1461-40F3-4621-A383-5FE9A849ADE2}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="2" max="2" width="34.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.1328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>22</v>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A2">
+        <f>A3-30</f>
+        <v>1960</v>
+      </c>
+      <c r="B2" s="3">
+        <f>B3</f>
+        <v>1.4054861319724239</v>
+      </c>
+      <c r="C2" s="3">
+        <f>B2</f>
+        <v>1.4054861319724239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A3">
+        <f>A4-30</f>
+        <v>1990</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1.4054861319724239</v>
+      </c>
+      <c r="C3" s="3">
+        <f t="shared" ref="C3:C7" si="0">B3</f>
+        <v>1.4054861319724239</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A4">
+        <v>2020</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1.3396677627394229</v>
+      </c>
+      <c r="C4" s="3">
+        <f t="shared" si="0"/>
+        <v>1.3396677627394229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A5">
+        <f>A4+30</f>
+        <v>2050</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1.1219986438186136</v>
+      </c>
+      <c r="C5" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1219986438186136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A6">
+        <f t="shared" ref="A6:A7" si="1">A5+30</f>
+        <v>2080</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1.0688804499803877</v>
+      </c>
+      <c r="C6" s="3">
+        <f t="shared" si="0"/>
+        <v>1.0688804499803877</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A7">
+        <f t="shared" si="1"/>
+        <v>2110</v>
+      </c>
+      <c r="B7" s="3">
+        <f>B6</f>
+        <v>1.0688804499803877</v>
+      </c>
+      <c r="C7" s="3">
+        <f t="shared" si="0"/>
+        <v>1.0688804499803877</v>
       </c>
     </row>
   </sheetData>
@@ -525,121 +586,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D43B1461-40F3-4621-A383-5FE9A849ADE2}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE76B0EF-4908-4CB2-98A8-B49EE220FB32}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="2" max="2" width="34.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.40625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <f>A3-30</f>
-        <v>1960</v>
-      </c>
-      <c r="B2" s="3">
-        <f>B3</f>
-        <v>1.4054861319724239</v>
-      </c>
-      <c r="C2" s="3">
-        <f>B2</f>
-        <v>1.4054861319724239</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <f>A4-30</f>
-        <v>1990</v>
-      </c>
-      <c r="B3" s="3">
-        <v>1.4054861319724239</v>
-      </c>
-      <c r="C3" s="3">
-        <f t="shared" ref="C3:C7" si="0">B3</f>
-        <v>1.4054861319724239</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2020</v>
-      </c>
-      <c r="B4" s="3">
-        <v>1.3396677627394229</v>
-      </c>
-      <c r="C4" s="3">
-        <f t="shared" si="0"/>
-        <v>1.3396677627394229</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <f>A4+30</f>
-        <v>2050</v>
-      </c>
-      <c r="B5" s="3">
-        <v>1.1219986438186136</v>
-      </c>
-      <c r="C5" s="3">
-        <f t="shared" si="0"/>
-        <v>1.1219986438186136</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <f t="shared" ref="A6:A7" si="1">A5+30</f>
-        <v>2080</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1.0688804499803877</v>
-      </c>
-      <c r="C6" s="3">
-        <f t="shared" si="0"/>
-        <v>1.0688804499803877</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <f t="shared" si="1"/>
-        <v>2110</v>
-      </c>
-      <c r="B7" s="3">
-        <f>B6</f>
-        <v>1.0688804499803877</v>
-      </c>
-      <c r="C7" s="3">
-        <f t="shared" si="0"/>
-        <v>1.0688804499803877</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE76B0EF-4908-4CB2-98A8-B49EE220FB32}">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -659,7 +616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A2">
         <v>0</v>
       </c>
@@ -679,7 +636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A3">
         <v>1</v>
       </c>
@@ -701,7 +658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A4">
         <v>2</v>
       </c>
@@ -722,7 +679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.75">
       <c r="A5">
         <v>3</v>
       </c>
@@ -750,23 +707,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E48DC5-CA22-4A6E-BD10-69F2BD6158FF}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.140625" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.40625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1328125" customWidth="1"/>
+    <col min="9" max="9" width="17.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -792,10 +749,10 @@
         <v>13</v>
       </c>
       <c r="I1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.75">
       <c r="A2">
         <v>2020</v>
       </c>
